--- a/EIANN/data/FigT6_mnist_hyperparams_part1.xlsx
+++ b/EIANN/data/FigT6_mnist_hyperparams_part1.xlsx
@@ -510,7 +510,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Wη (H1)</t>
+          <t>η, W (H1)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -574,7 +574,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wη (H2)</t>
+          <t>η, W (H2)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -634,7 +634,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Wη (Output)</t>
+          <t>η, W (Output)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1118,7 +1118,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Yη (SomaI, H1)</t>
+          <t>η, Y (SomaI, H1)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1156,7 +1156,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Wη (SomaI, H1)</t>
+          <t>η, W (SomaI, H1)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1194,7 +1194,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Qη (SomaI, H1)</t>
+          <t>η, Q (SomaI, H1)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1232,7 +1232,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rη (SomaI, H1)</t>
+          <t>η, R (SomaI, H1)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1270,7 +1270,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Yη (SomaI, H2)</t>
+          <t>η, Y (SomaI, H2)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1308,7 +1308,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wη (SomaI, H2)</t>
+          <t>η, W (SomaI, H2)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1346,7 +1346,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Qη (SomaI, H2)</t>
+          <t>η, Q (SomaI, H2)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1384,7 +1384,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rη (SomaI, H2)</t>
+          <t>η, R (SomaI, H2)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1422,7 +1422,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Yη (SomaI, Output)</t>
+          <t>η, Y (SomaI, Output)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1460,7 +1460,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Wη (SomaI, Output)</t>
+          <t>η, W (SomaI, Output)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1498,7 +1498,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Qη (SomaI, Output)</t>
+          <t>η, Q (SomaI, Output)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1536,7 +1536,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Rη (SomaI, Output)</t>
+          <t>η, R (SomaI, Output)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1574,7 +1574,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WΣ (H1)</t>
+          <t>Wsum (H1)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1614,7 +1614,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>YΣ (SomaI, H1)</t>
+          <t>Ysum (SomaI, H1)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1654,7 +1654,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WΣ (SomaI, H1)</t>
+          <t>Wsum (SomaI, H1)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QΣ (SomaI, H1)</t>
+          <t>Qsum (SomaI, H1)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RΣ (SomaI, H1)</t>
+          <t>Rsum (SomaI, H1)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1774,7 +1774,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WΣ (H2)</t>
+          <t>Wsum (H2)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1814,7 +1814,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>YΣ (SomaI, H2)</t>
+          <t>Ysum (SomaI, H2)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1854,7 +1854,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>WΣ (SomaI, H2)</t>
+          <t>Wsum (SomaI, H2)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1894,7 +1894,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QΣ (SomaI, H2)</t>
+          <t>Qsum (SomaI, H2)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1934,7 +1934,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>RΣ (SomaI, H2)</t>
+          <t>Rsum (SomaI, H2)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1974,7 +1974,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>YΣ (SomaI, Output)</t>
+          <t>Ysum (SomaI, Output)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2014,7 +2014,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>WΣ (SomaI, Output)</t>
+          <t>Wsum (SomaI, Output)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2054,7 +2054,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QΣ (SomaI, Output)</t>
+          <t>Qsum (SomaI, Output)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2094,7 +2094,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RΣ (SomaI, Output)</t>
+          <t>Rsum (SomaI, Output)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
